--- a/experiment/HAT_bestx4/Test/results_table.xlsx
+++ b/experiment/HAT_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.219/
-0.8935</t>
+          <t>32.267/
+0.8941</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.618/
-0.7820</t>
+          <t>28.633/
+0.7825</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.589/
-0.7375</t>
+          <t>27.601/
+0.7379</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>26.037/
-0.7851</t>
+          <t>26.081/
+0.7863</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.488/
-0.9089</t>
+          <t>30.550/
+0.9096</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>28.990/
-0.8214</t>
+          <t>29.026/
+0.8221</t>
         </is>
       </c>
     </row>
